--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -2894,7 +2894,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -2902,13 +2902,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0F172A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2923,8 +2932,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3267,20 +3277,23 @@
   <dimension ref="A1:D471"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="25" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
